--- a/excel/day_routine.xlsx
+++ b/excel/day_routine.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -509,8 +509,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="16.85546875" customWidth="1"/>
+    <col min="2" max="2" width="30.42578125" customWidth="1"/>
+    <col min="3" max="3" width="17.85546875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
@@ -625,73 +630,73 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
-      <c r="A14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" t="s">
-        <v>34</v>
-      </c>
-    </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>35</v>
+      </c>
+      <c r="C16" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
         <v>21</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B22" t="s">
         <v>41</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C22" t="s">
         <v>45</v>
       </c>
     </row>

--- a/excel/day_routine.xlsx
+++ b/excel/day_routine.xlsx
@@ -158,7 +158,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -174,13 +174,25 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -193,31 +205,33 @@
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color rgb="FFB2B2B2"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color rgb="FFB2B2B2"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Note" xfId="1" builtinId="10"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>

--- a/excel/day_routine.xlsx
+++ b/excel/day_routine.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>Time</t>
   </si>
@@ -25,69 +25,15 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>5:00 AM</t>
-  </si>
-  <si>
-    <t>5:05 AM</t>
-  </si>
-  <si>
-    <t>5:10 AM</t>
-  </si>
-  <si>
-    <t>5:15 AM</t>
-  </si>
-  <si>
-    <t>5:35 AM</t>
-  </si>
-  <si>
-    <t>5:50 AM</t>
-  </si>
-  <si>
-    <t>6:05 AM</t>
-  </si>
-  <si>
-    <t>7:05 AM</t>
-  </si>
-  <si>
-    <t>7:30 AM</t>
-  </si>
-  <si>
-    <t>7:40 AM</t>
-  </si>
-  <si>
-    <t>8:40 AM</t>
-  </si>
-  <si>
     <t>2:00 PM</t>
   </si>
   <si>
-    <t>3:00 PM</t>
-  </si>
-  <si>
     <t>3:45 PM</t>
   </si>
   <si>
     <t>4:15 PM</t>
   </si>
   <si>
-    <t>7:45 PM</t>
-  </si>
-  <si>
-    <t>8:30 PM</t>
-  </si>
-  <si>
-    <t>9:00 PM</t>
-  </si>
-  <si>
-    <t>9:30 PM</t>
-  </si>
-  <si>
-    <t>Wake up and make bed</t>
-  </si>
-  <si>
-    <t>Drink 2 glasses of water</t>
-  </si>
-  <si>
     <t>Sit silently and deep breathe</t>
   </si>
   <si>
@@ -97,21 +43,12 @@
     <t>Oil pulling and brushing</t>
   </si>
   <si>
-    <t>Daily abs</t>
-  </si>
-  <si>
     <t>If needed: Self-care</t>
   </si>
   <si>
-    <t>Skincare and bathing</t>
-  </si>
-  <si>
     <t>Prepare breakfast and eat</t>
   </si>
   <si>
-    <t>Hair care</t>
-  </si>
-  <si>
     <t>Learn a new skill</t>
   </si>
   <si>
@@ -130,9 +67,6 @@
     <t>Go for training</t>
   </si>
   <si>
-    <t>Come back, freshen up, and prepare rice</t>
-  </si>
-  <si>
     <t>Dinner and schedule the next day</t>
   </si>
   <si>
@@ -152,6 +86,21 @@
   </si>
   <si>
     <t>Before this time</t>
+  </si>
+  <si>
+    <t>Wake up / Drink 2 glasses of water / Make Bed</t>
+  </si>
+  <si>
+    <t>Physical Activity</t>
+  </si>
+  <si>
+    <t>Skin Care, Hair care</t>
+  </si>
+  <si>
+    <t>Pre Skincare, Hair Care and Bathing</t>
+  </si>
+  <si>
+    <t>Come back, fresh up, and prepare rice</t>
   </si>
 </sst>
 </file>
@@ -223,10 +172,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -527,7 +488,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.85546875" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" customWidth="1"/>
+    <col min="2" max="2" width="41" customWidth="1"/>
     <col min="3" max="3" width="17.85546875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -543,175 +504,184 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" t="s">
+      <c r="A2" s="5">
+        <v>0.20486111111111113</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="3"/>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="2">
+        <v>0.21180555555555555</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="3"/>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="2">
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="3"/>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="2">
+        <v>0.23263888888888887</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="3"/>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="2">
+        <v>0.23611111111111113</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="3"/>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="2">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="3"/>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="3"/>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="2">
+        <v>0.32291666666666669</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="2">
+        <v>0.36458333333333331</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="3"/>
+      <c r="C13" s="3"/>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" s="3"/>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
+    <row r="17" spans="1:3">
+      <c r="A17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B17" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="3"/>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="3"/>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="2">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" s="3"/>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="3"/>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="2">
+        <v>0.875</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="3"/>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>35</v>
-      </c>
-      <c r="C16" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" t="s">
-        <v>17</v>
-      </c>
-      <c r="B18" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" t="s">
-        <v>19</v>
-      </c>
-      <c r="B20" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" t="s">
-        <v>20</v>
-      </c>
-      <c r="B21" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" t="s">
-        <v>21</v>
-      </c>
-      <c r="B22" t="s">
-        <v>41</v>
-      </c>
-      <c r="C22" t="s">
-        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/excel/day_routine.xlsx
+++ b/excel/day_routine.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>Time</t>
   </si>
@@ -101,6 +101,9 @@
   </si>
   <si>
     <t>Come back, fresh up, and prepare rice</t>
+  </si>
+  <si>
+    <t>4:55 AM</t>
   </si>
 </sst>
 </file>
@@ -186,7 +189,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -504,8 +507,8 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="5">
-        <v>0.20486111111111113</v>
+      <c r="A2" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>24</v>

--- a/excel/day_routine.xlsx
+++ b/excel/day_routine.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>Time</t>
   </si>
@@ -103,7 +103,10 @@
     <t>Come back, fresh up, and prepare rice</t>
   </si>
   <si>
-    <t>4:55 AM</t>
+    <t xml:space="preserve">4:55 </t>
+  </si>
+  <si>
+    <t>e</t>
   </si>
 </sst>
 </file>
@@ -513,7 +516,9 @@
       <c r="B2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="3"/>
+      <c r="C2" s="3" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2">

--- a/excel/day_routine.xlsx
+++ b/excel/day_routine.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="44">
   <si>
     <t>Time</t>
   </si>
@@ -103,10 +103,49 @@
     <t>Come back, fresh up, and prepare rice</t>
   </si>
   <si>
-    <t xml:space="preserve">4:55 </t>
-  </si>
-  <si>
-    <t>e</t>
+    <t>9:30 PM</t>
+  </si>
+  <si>
+    <t>9:00 PM</t>
+  </si>
+  <si>
+    <t>8:30 PM</t>
+  </si>
+  <si>
+    <t>7:45 PM</t>
+  </si>
+  <si>
+    <t>3:00 PM</t>
+  </si>
+  <si>
+    <t>8:45 AM</t>
+  </si>
+  <si>
+    <t>7:45 AM</t>
+  </si>
+  <si>
+    <t>7:30 AM</t>
+  </si>
+  <si>
+    <t>7:00 AM</t>
+  </si>
+  <si>
+    <t>6:00 AM</t>
+  </si>
+  <si>
+    <t>5:40 AM</t>
+  </si>
+  <si>
+    <t>5:20 AM</t>
+  </si>
+  <si>
+    <t>5:35 AM</t>
+  </si>
+  <si>
+    <t>5:05 AM</t>
+  </si>
+  <si>
+    <t>4:55 AM</t>
   </si>
 </sst>
 </file>
@@ -178,13 +217,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -193,6 +229,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -510,185 +552,183 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="2"/>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2"/>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2"/>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="2"/>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="2"/>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="2"/>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="2"/>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="2"/>
+      <c r="C13" s="2"/>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" s="2"/>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="2"/>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="2"/>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" s="2"/>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="2"/>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="2"/>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="2">
-        <v>0.21180555555555555</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="3"/>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="2">
-        <v>0.22222222222222221</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="3"/>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="2">
-        <v>0.23263888888888887</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="3"/>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="2">
-        <v>0.23611111111111113</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="3"/>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="2">
-        <v>0.29166666666666669</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="3"/>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="2">
-        <v>0.3125</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" s="3"/>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="2">
-        <v>0.32291666666666669</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="2">
-        <v>0.36458333333333331</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="3"/>
-      <c r="C13" s="3"/>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C15" s="3"/>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="2">
-        <v>0.625</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C17" s="3"/>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" s="3"/>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="2">
-        <v>0.82291666666666663</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C19" s="3"/>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="2">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C20" s="3"/>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="2">
-        <v>0.875</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C21" s="3"/>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="2">
-        <v>0.89583333333333337</v>
-      </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="2" t="s">
         <v>23</v>
       </c>
     </row>

--- a/excel/day_routine.xlsx
+++ b/excel/day_routine.xlsx
@@ -8,13 +8,14 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="43">
   <si>
     <t>Time</t>
   </si>
@@ -79,21 +80,12 @@
     <t>Optional</t>
   </si>
   <si>
-    <t>1-hour duration</t>
-  </si>
-  <si>
     <t>45 minutes</t>
   </si>
   <si>
-    <t>Before this time</t>
-  </si>
-  <si>
     <t>Wake up / Drink 2 glasses of water / Make Bed</t>
   </si>
   <si>
-    <t>Physical Activity</t>
-  </si>
-  <si>
     <t>Skin Care, Hair care</t>
   </si>
   <si>
@@ -121,18 +113,6 @@
     <t>8:45 AM</t>
   </si>
   <si>
-    <t>7:45 AM</t>
-  </si>
-  <si>
-    <t>7:30 AM</t>
-  </si>
-  <si>
-    <t>7:00 AM</t>
-  </si>
-  <si>
-    <t>6:00 AM</t>
-  </si>
-  <si>
     <t>5:40 AM</t>
   </si>
   <si>
@@ -146,6 +126,24 @@
   </si>
   <si>
     <t>4:55 AM</t>
+  </si>
+  <si>
+    <t>Jogging</t>
+  </si>
+  <si>
+    <t>6:40 AM</t>
+  </si>
+  <si>
+    <t>7:40 AM</t>
+  </si>
+  <si>
+    <t>8:10 AM</t>
+  </si>
+  <si>
+    <t>8:25 AM</t>
+  </si>
+  <si>
+    <t>Before 11.00 pm</t>
   </si>
 </sst>
 </file>
@@ -553,16 +551,16 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="4" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C2" s="2"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="5" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>7</v>
@@ -571,7 +569,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="5" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>8</v>
@@ -580,7 +578,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>6</v>
@@ -589,10 +587,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="5" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="C6" s="2"/>
     </row>
@@ -612,12 +610,12 @@
         <v>38</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>10</v>
@@ -626,27 +624,25 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="5" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C10" s="2"/>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="5" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>21</v>
-      </c>
+      <c r="C11" s="2"/>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
@@ -667,13 +663,13 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -696,16 +692,16 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="5" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C19" s="2"/>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="5" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>17</v>
@@ -714,7 +710,7 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="5" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>18</v>
@@ -723,16 +719,25 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/excel/day_routine.xlsx
+++ b/excel/day_routine.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>Time</t>
   </si>
@@ -23,9 +23,6 @@
     <t>Task</t>
   </si>
   <si>
-    <t>Notes</t>
-  </si>
-  <si>
     <t>2:00 PM</t>
   </si>
   <si>
@@ -35,18 +32,6 @@
     <t>4:15 PM</t>
   </si>
   <si>
-    <t>Sit silently and deep breathe</t>
-  </si>
-  <si>
-    <t>Restroom and track weight</t>
-  </si>
-  <si>
-    <t>Oil pulling and brushing</t>
-  </si>
-  <si>
-    <t>If needed: Self-care</t>
-  </si>
-  <si>
     <t>Prepare breakfast and eat</t>
   </si>
   <si>
@@ -74,24 +59,6 @@
     <t>Prepare for sleep</t>
   </si>
   <si>
-    <t>Sleep</t>
-  </si>
-  <si>
-    <t>Optional</t>
-  </si>
-  <si>
-    <t>45 minutes</t>
-  </si>
-  <si>
-    <t>Wake up / Drink 2 glasses of water / Make Bed</t>
-  </si>
-  <si>
-    <t>Skin Care, Hair care</t>
-  </si>
-  <si>
-    <t>Pre Skincare, Hair Care and Bathing</t>
-  </si>
-  <si>
     <t>Come back, fresh up, and prepare rice</t>
   </si>
   <si>
@@ -110,18 +77,6 @@
     <t>3:00 PM</t>
   </si>
   <si>
-    <t>8:45 AM</t>
-  </si>
-  <si>
-    <t>5:40 AM</t>
-  </si>
-  <si>
-    <t>5:20 AM</t>
-  </si>
-  <si>
-    <t>5:35 AM</t>
-  </si>
-  <si>
     <t>5:05 AM</t>
   </si>
   <si>
@@ -131,19 +86,49 @@
     <t>Jogging</t>
   </si>
   <si>
-    <t>6:40 AM</t>
-  </si>
-  <si>
-    <t>7:40 AM</t>
-  </si>
-  <si>
-    <t>8:10 AM</t>
-  </si>
-  <si>
-    <t>8:25 AM</t>
-  </si>
-  <si>
-    <t>Before 11.00 pm</t>
+    <t>5.00 AM</t>
+  </si>
+  <si>
+    <t>Wake up</t>
+  </si>
+  <si>
+    <t>Track weight / Drink 2 glasses of water</t>
+  </si>
+  <si>
+    <t>Get ready for the Jogging</t>
+  </si>
+  <si>
+    <t>5:10 AM</t>
+  </si>
+  <si>
+    <t>Oil Pulling / Brushing</t>
+  </si>
+  <si>
+    <t>6:10 AM</t>
+  </si>
+  <si>
+    <t>Stretch</t>
+  </si>
+  <si>
+    <t>6:20 AM</t>
+  </si>
+  <si>
+    <t>6.35 AM</t>
+  </si>
+  <si>
+    <t>7:00 AM</t>
+  </si>
+  <si>
+    <t>Self Care and Fresh up</t>
+  </si>
+  <si>
+    <t>8.45 AM</t>
+  </si>
+  <si>
+    <t>8:15 AM</t>
+  </si>
+  <si>
+    <t>Meditation Before Sleep (Before 11.00 pm)</t>
   </si>
 </sst>
 </file>
@@ -530,7 +515,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.85546875" customWidth="1"/>
@@ -545,188 +530,170 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="4" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C2" s="2"/>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="5" t="s">
-        <v>35</v>
+      <c r="A3" s="6" t="s">
+        <v>23</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="2"/>
+        <v>25</v>
+      </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="5" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="C4" s="2"/>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="5" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C5" s="2"/>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>37</v>
+        <v>29</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="C6" s="2"/>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>20</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="2"/>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="5" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="C9" s="2"/>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="5" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="2"/>
+        <v>6</v>
+      </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="5" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C11" s="2"/>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>12</v>
-      </c>
+      <c r="A12" s="5"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="2"/>
+      <c r="A13" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="C13" s="2"/>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="2"/>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="6" t="s">
         <v>3</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" s="2"/>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="5" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="2"/>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>14</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>15</v>
       </c>
       <c r="C17" s="2"/>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="5" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C18" s="2"/>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="5" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="C19" s="2"/>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="5" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="C20" s="2"/>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C21" s="2"/>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>42</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
